--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300936</v>
+        <v>123300935</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599863</v>
+        <v>599893</v>
       </c>
       <c r="R2" t="n">
-        <v>6890832</v>
+        <v>6890866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300934</v>
+        <v>123300937</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +817,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599872</v>
+        <v>599868</v>
       </c>
       <c r="R3" t="n">
-        <v>6890838</v>
+        <v>6890798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300937</v>
+        <v>123300934</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,47 +947,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599868</v>
+        <v>599872</v>
       </c>
       <c r="R4" t="n">
-        <v>6890798</v>
+        <v>6890838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300935</v>
+        <v>123300936</v>
       </c>
       <c r="B5" t="n">
-        <v>98282</v>
+        <v>79851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,35 +1068,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599893</v>
+        <v>599863</v>
       </c>
       <c r="R5" t="n">
-        <v>6890866</v>
+        <v>6890832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300935</v>
+        <v>123300936</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599893</v>
+        <v>599863</v>
       </c>
       <c r="R2" t="n">
-        <v>6890866</v>
+        <v>6890832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300937</v>
+        <v>123300935</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599868</v>
+        <v>599893</v>
       </c>
       <c r="R3" t="n">
-        <v>6890798</v>
+        <v>6890866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300934</v>
+        <v>123300937</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,38 +947,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599872</v>
+        <v>599868</v>
       </c>
       <c r="R4" t="n">
-        <v>6890838</v>
+        <v>6890798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300936</v>
+        <v>123300934</v>
       </c>
       <c r="B5" t="n">
-        <v>79851</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,43 +1081,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599863</v>
+        <v>599872</v>
       </c>
       <c r="R5" t="n">
-        <v>6890832</v>
+        <v>6890838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123300936</v>
       </c>
       <c r="B2" t="n">
-        <v>79853</v>
+        <v>79854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123300935</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>98293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>123300934</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300936</v>
+        <v>123300937</v>
       </c>
       <c r="B2" t="n">
-        <v>79854</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599863</v>
+        <v>599868</v>
       </c>
       <c r="R2" t="n">
-        <v>6890832</v>
+        <v>6890798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300935</v>
+        <v>123300934</v>
       </c>
       <c r="B3" t="n">
-        <v>98293</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,47 +817,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599893</v>
+        <v>599872</v>
       </c>
       <c r="R3" t="n">
-        <v>6890866</v>
+        <v>6890838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300937</v>
+        <v>123300935</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>98296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,31 +942,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599868</v>
+        <v>599893</v>
       </c>
       <c r="R4" t="n">
-        <v>6890798</v>
+        <v>6890866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300934</v>
+        <v>123300936</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>79857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,34 +1072,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599872</v>
+        <v>599863</v>
       </c>
       <c r="R5" t="n">
-        <v>6890838</v>
+        <v>6890832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123300937</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123300934</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>123300935</v>
       </c>
       <c r="B4" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>123300936</v>
       </c>
       <c r="B5" t="n">
-        <v>79857</v>
+        <v>79863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123300937</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300934</v>
+        <v>123300935</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +817,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599872</v>
+        <v>599893</v>
       </c>
       <c r="R3" t="n">
-        <v>6890838</v>
+        <v>6890866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300935</v>
+        <v>123300934</v>
       </c>
       <c r="B4" t="n">
-        <v>98313</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,47 +947,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599893</v>
+        <v>599872</v>
       </c>
       <c r="R4" t="n">
-        <v>6890866</v>
+        <v>6890838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
         <v>123300936</v>
       </c>
       <c r="B5" t="n">
-        <v>79863</v>
+        <v>79868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300937</v>
+        <v>123300934</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599868</v>
+        <v>599872</v>
       </c>
       <c r="R2" t="n">
-        <v>6890798</v>
+        <v>6890838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,7 +799,7 @@
         <v>123300935</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300934</v>
+        <v>123300937</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,38 +938,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599872</v>
+        <v>599868</v>
       </c>
       <c r="R4" t="n">
-        <v>6890838</v>
+        <v>6890798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
         <v>123300936</v>
       </c>
       <c r="B5" t="n">
-        <v>79868</v>
+        <v>79870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300934</v>
+        <v>123300937</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599872</v>
+        <v>599868</v>
       </c>
       <c r="R2" t="n">
-        <v>6890838</v>
+        <v>6890798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300935</v>
+        <v>123300934</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +817,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599893</v>
+        <v>599872</v>
       </c>
       <c r="R3" t="n">
-        <v>6890866</v>
+        <v>6890838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300937</v>
+        <v>123300935</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,31 +942,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599868</v>
+        <v>599893</v>
       </c>
       <c r="R4" t="n">
-        <v>6890798</v>
+        <v>6890866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300937</v>
+        <v>123300936</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599868</v>
+        <v>599863</v>
       </c>
       <c r="R2" t="n">
-        <v>6890798</v>
+        <v>6890832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300934</v>
+        <v>123300937</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,38 +817,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599872</v>
+        <v>599868</v>
       </c>
       <c r="R3" t="n">
-        <v>6890838</v>
+        <v>6890798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -885,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1056,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300936</v>
+        <v>123300934</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,43 +1081,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599863</v>
+        <v>599872</v>
       </c>
       <c r="R5" t="n">
-        <v>6890832</v>
+        <v>6890838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300936</v>
+        <v>123300937</v>
       </c>
       <c r="B2" t="n">
-        <v>79870</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599863</v>
+        <v>599868</v>
       </c>
       <c r="R2" t="n">
-        <v>6890832</v>
+        <v>6890798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300937</v>
+        <v>123300936</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599868</v>
+        <v>599863</v>
       </c>
       <c r="R3" t="n">
-        <v>6890798</v>
+        <v>6890832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300935</v>
+        <v>123300934</v>
       </c>
       <c r="B4" t="n">
-        <v>97996</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,47 +947,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599893</v>
+        <v>599872</v>
       </c>
       <c r="R4" t="n">
-        <v>6890866</v>
+        <v>6890838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300934</v>
+        <v>123300935</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,38 +1068,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599872</v>
+        <v>599893</v>
       </c>
       <c r="R5" t="n">
-        <v>6890838</v>
+        <v>6890866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18976-2023 artfynd.xlsx
+++ b/artfynd/A 18976-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300937</v>
+        <v>123300936</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599868</v>
+        <v>599863</v>
       </c>
       <c r="R2" t="n">
-        <v>6890798</v>
+        <v>6890832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>947</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300936</v>
+        <v>123300934</v>
       </c>
       <c r="B3" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,43 +821,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599863</v>
+        <v>599872</v>
       </c>
       <c r="R3" t="n">
-        <v>6890832</v>
+        <v>6890838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +875,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300934</v>
+        <v>123300935</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,38 +938,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyran, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599872</v>
+        <v>599893</v>
       </c>
       <c r="R4" t="n">
-        <v>6890838</v>
+        <v>6890866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>949</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300935</v>
+        <v>123300937</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,31 +1072,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599893</v>
+        <v>599868</v>
       </c>
       <c r="R5" t="n">
-        <v>6890866</v>
+        <v>6890798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>946</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
